--- a/relatorios/contabilidade/RELATORIO_HOLERITE_SETEMBRO_2026_CENTRO_pgto_05-10-2026.xlsx
+++ b/relatorios/contabilidade/RELATORIO_HOLERITE_SETEMBRO_2026_CENTRO_pgto_05-10-2026.xlsx
@@ -2104,9 +2104,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15">
-        <f> COMISSÃO TOTAL</f>
-        <v/>
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>COMISSÃO TOTAL (soma)</t>
+        </is>
       </c>
       <c r="B11" s="20">
         <f>SUM(B9:B10)</f>
@@ -2176,9 +2177,10 @@
         <f>SUM(B12:G12)</f>
         <v/>
       </c>
-      <c r="I12" s="33">
-        <f> (comissão total + horas extras) × (4 domingos + feriado 07/09) ÷ 25 dias úteis de setembro/2026.</f>
-        <v/>
+      <c r="I12" s="33" t="inlineStr">
+        <is>
+          <t>Cálculo: (comissão total + horas extras) × (4 domingos + feriado 07/09) ÷ 25 dias úteis de setembro/2026.</t>
+        </is>
       </c>
     </row>
     <row r="13">

--- a/relatorios/contabilidade/RELATORIO_HOLERITE_SETEMBRO_2026_CENTRO_pgto_05-10-2026.xlsx
+++ b/relatorios/contabilidade/RELATORIO_HOLERITE_SETEMBRO_2026_CENTRO_pgto_05-10-2026.xlsx
@@ -18,10 +18,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'BASE INOVAFARMA SET.26'!$A$4:$J$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'HOLERITE SET.26'!$A$4:$I$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'HOLERITE SET.26'!$A$4:$I$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'LISTA CONTABILIDADE'!$A$4:$E$153</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'GANHOS DO COLABORADOR'!$A$1:$D$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PONTO SET.26'!$A$4:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PONTO SET.26'!$A$4:$I$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'FOLGUISTAS'!$A$4:$H$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -667,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -844,26 +844,22 @@
       <c r="A24" s="4" t="inlineStr"/>
       <c r="B24" s="5" t="inlineStr">
         <is>
+          <t>RENALDO: férias de 01 a 30/09/2026 (mês inteiro) — salário zerado e sem desconto de vale-transporte; férias e 1/3 em recibo próprio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="17" customHeight="1">
+      <c r="A25" s="4" t="inlineStr"/>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
           <t>SERGIO e ANA CELIA seguem como folguistas (diária de R$ 150,00 e R$ 100,00), na aba FOLGUISTAS.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>PENDÊNCIAS — CONFIRMAR ANTES DE ENVIAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>Horas extras, adicional noturno e feriados trabalhados de setembro — lançar na aba PONTO SET.26.</t>
         </is>
       </c>
     </row>
@@ -875,7 +871,7 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Prêmio cota geral e prêmio pré-vencidos, conforme a tabela de metas da loja.</t>
+          <t>Horas extras, adicional noturno e feriados trabalhados de setembro — lançar na aba PONTO SET.26.</t>
         </is>
       </c>
     </row>
@@ -887,7 +883,7 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Vales adiantados, convênio e faltas de agosto.</t>
+          <t>Prêmio cota geral e prêmio pré-vencidos, conforme a tabela de metas da loja.</t>
         </is>
       </c>
     </row>
@@ -899,7 +895,7 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Férias, afastamentos e admissões que mudem o salário do mês.</t>
+          <t>Vales adiantados, convênio e faltas de agosto.</t>
         </is>
       </c>
     </row>
@@ -911,7 +907,7 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Extrair o relatório de comissões de setembro no InovaFarma e preencher a aba BASE INOVAFARMA SET.26.</t>
+          <t>Férias, afastamentos e admissões que mudem o salário do mês.</t>
         </is>
       </c>
     </row>
@@ -923,37 +919,41 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
+          <t>Extrair o relatório de comissões de setembro no InovaFarma e preencher a aba BASE INOVAFARMA SET.26.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="17" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
           <t>Preencher a quantidade de diárias de SERGIO e ANA CELIA.</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>OBSERVAÇÃO TÉCNICA</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="4" t="inlineStr"/>
-      <c r="B33" s="5" t="inlineStr">
+    <row r="34" ht="17" customHeight="1">
+      <c r="A34" s="4" t="inlineStr"/>
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>As células de total e de cálculo são fórmulas. Ao abrir no Excel ou no Google Planilhas elas aparecem calculadas; em visualizadores simples podem aparecer em branco até o arquivo ser aberto.</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>ABAS DO ARQUIVO</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="4" t="inlineStr"/>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>HOLERITE SET.26 — relatório principal da competência setembro/2026.</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       <c r="A36" s="4" t="inlineStr"/>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>GANHOS DO COLABORADOR — demonstrativo individual, pronto para imprimir/mandar.</t>
+          <t>HOLERITE SET.26 — relatório principal da competência setembro/2026.</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
       <c r="A37" s="4" t="inlineStr"/>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>LISTA CONTABILIDADE — os mesmos lançamentos em formato de lista.</t>
+          <t>GANHOS DO COLABORADOR — demonstrativo individual, pronto para imprimir/mandar.</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       <c r="A38" s="4" t="inlineStr"/>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>BASE INOVAFARMA SET.26 — apuração de comissões e incentivos por vendedor.</t>
+          <t>LISTA CONTABILIDADE — os mesmos lançamentos em formato de lista.</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
       <c r="A39" s="4" t="inlineStr"/>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>PARÂMETROS — calendário do mês, fator do DSR e valores fixos.</t>
+          <t>BASE INOVAFARMA SET.26 — apuração de comissões e incentivos por vendedor.</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       <c r="A40" s="4" t="inlineStr"/>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>PONTO SET.26 — horas extras, adicional noturno e feriado trabalhado; alimenta o holerite.</t>
+          <t>PARÂMETROS — calendário do mês, fator do DSR e valores fixos.</t>
         </is>
       </c>
     </row>
@@ -1001,6 +1001,14 @@
       <c r="A41" s="4" t="inlineStr"/>
       <c r="B41" s="5" t="inlineStr">
         <is>
+          <t>PONTO SET.26 — horas extras, adicional noturno e feriado trabalhado; alimenta o holerite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="17" customHeight="1">
+      <c r="A42" s="4" t="inlineStr"/>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
           <t>FOLGUISTAS — diárias de SERGIO e ANA CELIA para o contas a pagar (fora do holerite).</t>
         </is>
       </c>
@@ -1008,14 +1016,14 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A26:B26"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A33:B33"/>
     <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A32:B32"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A35:B35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1839,7 +1847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1945,7 +1953,7 @@
         <v>1621</v>
       </c>
       <c r="E6" s="31" t="n">
-        <v>1621</v>
+        <v>0</v>
       </c>
       <c r="F6" s="31" t="n">
         <v>1621</v>
@@ -1970,27 +1978,27 @@
         </is>
       </c>
       <c r="B7" s="34">
-        <f>SUMIFS('PONTO SET.26'!$G$5:$G$13,'PONTO SET.26'!$A$5:$A$13,B$4,'PONTO SET.26'!$H$5:$H$13,"ADICIONAL NOTURNO")</f>
+        <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,B$4,'PONTO SET.26'!$H$5:$H$14,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
       <c r="C7" s="34">
-        <f>SUMIFS('PONTO SET.26'!$G$5:$G$13,'PONTO SET.26'!$A$5:$A$13,C$4,'PONTO SET.26'!$H$5:$H$13,"ADICIONAL NOTURNO")</f>
+        <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,C$4,'PONTO SET.26'!$H$5:$H$14,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
       <c r="D7" s="34">
-        <f>SUMIFS('PONTO SET.26'!$G$5:$G$13,'PONTO SET.26'!$A$5:$A$13,D$4,'PONTO SET.26'!$H$5:$H$13,"ADICIONAL NOTURNO")</f>
+        <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,D$4,'PONTO SET.26'!$H$5:$H$14,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
       <c r="E7" s="34">
-        <f>SUMIFS('PONTO SET.26'!$G$5:$G$13,'PONTO SET.26'!$A$5:$A$13,E$4,'PONTO SET.26'!$H$5:$H$13,"ADICIONAL NOTURNO")</f>
+        <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,E$4,'PONTO SET.26'!$H$5:$H$14,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
       <c r="F7" s="34">
-        <f>SUMIFS('PONTO SET.26'!$G$5:$G$13,'PONTO SET.26'!$A$5:$A$13,F$4,'PONTO SET.26'!$H$5:$H$13,"ADICIONAL NOTURNO")</f>
+        <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,F$4,'PONTO SET.26'!$H$5:$H$14,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
       <c r="G7" s="34">
-        <f>SUMIFS('PONTO SET.26'!$G$5:$G$13,'PONTO SET.26'!$A$5:$A$13,G$4,'PONTO SET.26'!$H$5:$H$13,"ADICIONAL NOTURNO")</f>
+        <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,G$4,'PONTO SET.26'!$H$5:$H$14,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
       <c r="H7" s="20">
@@ -2010,27 +2018,27 @@
         </is>
       </c>
       <c r="B8" s="34">
-        <f>SUMIFS('PONTO SET.26'!$G$5:$G$13,'PONTO SET.26'!$A$5:$A$13,B$4,'PONTO SET.26'!$H$5:$H$13,"HORAS EXTRAS")</f>
+        <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,B$4,'PONTO SET.26'!$H$5:$H$14,"HORAS EXTRAS")</f>
         <v/>
       </c>
       <c r="C8" s="34">
-        <f>SUMIFS('PONTO SET.26'!$G$5:$G$13,'PONTO SET.26'!$A$5:$A$13,C$4,'PONTO SET.26'!$H$5:$H$13,"HORAS EXTRAS")</f>
+        <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,C$4,'PONTO SET.26'!$H$5:$H$14,"HORAS EXTRAS")</f>
         <v/>
       </c>
       <c r="D8" s="34">
-        <f>SUMIFS('PONTO SET.26'!$G$5:$G$13,'PONTO SET.26'!$A$5:$A$13,D$4,'PONTO SET.26'!$H$5:$H$13,"HORAS EXTRAS")</f>
+        <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,D$4,'PONTO SET.26'!$H$5:$H$14,"HORAS EXTRAS")</f>
         <v/>
       </c>
       <c r="E8" s="34">
-        <f>SUMIFS('PONTO SET.26'!$G$5:$G$13,'PONTO SET.26'!$A$5:$A$13,E$4,'PONTO SET.26'!$H$5:$H$13,"HORAS EXTRAS")</f>
+        <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,E$4,'PONTO SET.26'!$H$5:$H$14,"HORAS EXTRAS")</f>
         <v/>
       </c>
       <c r="F8" s="34">
-        <f>SUMIFS('PONTO SET.26'!$G$5:$G$13,'PONTO SET.26'!$A$5:$A$13,F$4,'PONTO SET.26'!$H$5:$H$13,"HORAS EXTRAS")</f>
+        <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,F$4,'PONTO SET.26'!$H$5:$H$14,"HORAS EXTRAS")</f>
         <v/>
       </c>
       <c r="G8" s="34">
-        <f>SUMIFS('PONTO SET.26'!$G$5:$G$13,'PONTO SET.26'!$A$5:$A$13,G$4,'PONTO SET.26'!$H$5:$H$13,"HORAS EXTRAS")</f>
+        <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,G$4,'PONTO SET.26'!$H$5:$H$14,"HORAS EXTRAS")</f>
         <v/>
       </c>
       <c r="H8" s="20">
@@ -2493,7 +2501,7 @@
     <row r="24">
       <c r="A24" s="30" t="inlineStr">
         <is>
-          <t>ADIANTAMENTO / VALES</t>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
       <c r="B24" s="35" t="n"/>
@@ -2609,9 +2617,7 @@
       <c r="D28" s="31" t="n">
         <v>-84.29000000000001</v>
       </c>
-      <c r="E28" s="31" t="n">
-        <v>-74.29000000000001</v>
-      </c>
+      <c r="E28" s="31" t="n"/>
       <c r="F28" s="31" t="n">
         <v>-84.29000000000001</v>
       </c>
@@ -2820,70 +2826,92 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="21" t="inlineStr">
-        <is>
-          <t>LEGENDA</t>
-        </is>
-      </c>
-      <c r="B38" s="22" t="inlineStr"/>
+    <row r="37">
+      <c r="A37" s="30" t="inlineStr">
+        <is>
+          <t>FÉRIAS PAGAS À PARTE (CONTAS A PAGAR)</t>
+        </is>
+      </c>
+      <c r="B37" s="31" t="n"/>
+      <c r="C37" s="31" t="n"/>
+      <c r="D37" s="31" t="n"/>
+      <c r="E37" s="31" t="n"/>
+      <c r="F37" s="31" t="n"/>
+      <c r="G37" s="31" t="n"/>
+      <c r="H37" s="32">
+        <f>SUM(B37:G37)</f>
+        <v/>
+      </c>
+      <c r="I37" s="33" t="inlineStr">
+        <is>
+          <t>Recibo de férias pago fora do holerite — lembrete para o contas a pagar. RENALDO: férias de 01 a 30/09/2026 — informar o valor do recibo.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="21" t="inlineStr">
         <is>
-          <t>Célula amarela, texto azul</t>
-        </is>
-      </c>
-      <c r="B39" s="22" t="inlineStr">
-        <is>
-          <t>valor digitado — PREENCHER ou conferir antes de enviar.</t>
-        </is>
-      </c>
+          <t>LEGENDA</t>
+        </is>
+      </c>
+      <c r="B39" s="22" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="21" t="inlineStr">
         <is>
-          <t>Célula laranja</t>
+          <t>Célula amarela, texto azul</t>
         </is>
       </c>
       <c r="B40" s="22" t="inlineStr">
         <is>
-          <t>valor repetido de agosto/2026 — CONFERIR se continua válido em setembro.</t>
+          <t>valor digitado — PREENCHER ou conferir antes de enviar.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="21" t="inlineStr">
         <is>
-          <t>Texto verde</t>
+          <t>Célula laranja</t>
         </is>
       </c>
       <c r="B41" s="22" t="inlineStr">
         <is>
-          <t>valor puxado da aba BASE INOVAFARMA SET.26 (não digitar por cima).</t>
+          <t>valor repetido de agosto/2026 — CONFERIR se continua válido em setembro.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="21" t="inlineStr">
         <is>
+          <t>Texto verde</t>
+        </is>
+      </c>
+      <c r="B42" s="22" t="inlineStr">
+        <is>
+          <t>valor puxado da aba BASE INOVAFARMA SET.26 (não digitar por cima).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="21" t="inlineStr">
+        <is>
           <t>Texto preto em célula verde</t>
         </is>
       </c>
-      <c r="B42" s="22" t="inlineStr">
+      <c r="B43" s="22" t="inlineStr">
         <is>
           <t>resultado de fórmula — não alterar.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I36"/>
+  <autoFilter ref="A4:I37"/>
   <mergeCells count="7">
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="B39:I39"/>
-    <mergeCell ref="B38:I38"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="B42:I42"/>
+    <mergeCell ref="B43:I43"/>
     <mergeCell ref="B41:I41"/>
     <mergeCell ref="B40:I40"/>
   </mergeCells>
@@ -3286,7 +3314,7 @@
       </c>
       <c r="B20" s="30" t="inlineStr">
         <is>
-          <t>ADIANTAMENTO / VALES</t>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
       <c r="C20" s="30" t="inlineStr">
@@ -3814,7 +3842,7 @@
       </c>
       <c r="B45" s="30" t="inlineStr">
         <is>
-          <t>ADIANTAMENTO / VALES</t>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
       <c r="C45" s="30" t="inlineStr">
@@ -4342,7 +4370,7 @@
       </c>
       <c r="B70" s="30" t="inlineStr">
         <is>
-          <t>ADIANTAMENTO / VALES</t>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
       <c r="C70" s="30" t="inlineStr">
@@ -4870,7 +4898,7 @@
       </c>
       <c r="B95" s="30" t="inlineStr">
         <is>
-          <t>ADIANTAMENTO / VALES</t>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
       <c r="C95" s="30" t="inlineStr">
@@ -5398,7 +5426,7 @@
       </c>
       <c r="B120" s="30" t="inlineStr">
         <is>
-          <t>ADIANTAMENTO / VALES</t>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
       <c r="C120" s="30" t="inlineStr">
@@ -5926,7 +5954,7 @@
       </c>
       <c r="B145" s="30" t="inlineStr">
         <is>
-          <t>ADIANTAMENTO / VALES</t>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
       <c r="C145" s="30" t="inlineStr">
@@ -6358,7 +6386,7 @@
     <row r="23">
       <c r="B23" s="30" t="inlineStr">
         <is>
-          <t>Adiantamento / vales</t>
+          <t>Adiantamento salarial / vales</t>
         </is>
       </c>
       <c r="C23" s="34">
@@ -6567,7 +6595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6684,21 +6712,45 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="52" t="n"/>
-      <c r="B6" s="52" t="n"/>
-      <c r="C6" s="52" t="n"/>
-      <c r="D6" s="52" t="n"/>
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>RENALDO</t>
+        </is>
+      </c>
+      <c r="B6" s="30" t="inlineStr">
+        <is>
+          <t>Registro informativo</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>dias</t>
+        </is>
+      </c>
       <c r="E6" s="34">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$G$6,1,MATCH(A6,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
-      <c r="F6" s="35" t="n"/>
+      <c r="F6" s="36" t="n">
+        <v>0</v>
+      </c>
       <c r="G6" s="20">
         <f>ROUND(C6*F6,2)</f>
         <v/>
       </c>
-      <c r="H6" s="52" t="n"/>
-      <c r="I6" s="52" t="n"/>
+      <c r="H6" s="51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I6" s="33" t="inlineStr">
+        <is>
+          <t>Férias de 01 a 30/09/2026 — mês inteiro. Salário zerado no holerite; férias e 1/3 vão em recibo próprio.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="52" t="n"/>
@@ -6820,60 +6872,77 @@
       <c r="I13" s="52" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n"/>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="A14" s="52" t="n"/>
+      <c r="B14" s="52" t="n"/>
+      <c r="C14" s="52" t="n"/>
+      <c r="D14" s="52" t="n"/>
+      <c r="E14" s="34">
+        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$G$6,1,MATCH(A14,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F14" s="35" t="n"/>
+      <c r="G14" s="20">
+        <f>ROUND(C14*F14,2)</f>
+        <v/>
+      </c>
+      <c r="H14" s="52" t="n"/>
+      <c r="I14" s="52" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="n"/>
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C14" s="18" t="n"/>
-      <c r="D14" s="18" t="n"/>
-      <c r="E14" s="18" t="n"/>
-      <c r="F14" s="18" t="n"/>
-      <c r="G14" s="20">
-        <f>SUM(G5:G13)</f>
-        <v/>
-      </c>
-      <c r="H14" s="18" t="n"/>
-      <c r="I14" s="18" t="n"/>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>Salário-hora = salário base ÷ 220. Hora extra = salário-hora × 1,5. Adicional noturno = salário-hora × 20%. Feriado trabalhado sem folga = 1 salário-dia a mais (salário base ÷ 30).</t>
-        </is>
-      </c>
+      <c r="C15" s="18" t="n"/>
+      <c r="D15" s="18" t="n"/>
+      <c r="E15" s="18" t="n"/>
+      <c r="F15" s="18" t="n"/>
+      <c r="G15" s="20">
+        <f>SUM(G5:G14)</f>
+        <v/>
+      </c>
+      <c r="H15" s="18" t="n"/>
+      <c r="I15" s="18" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>No salário de R$ 1.621,00: 40 horas extras dão R$ 442,09 e 24 horas dão R$ 265,25 — é a mesma conta usada na planilha de julho.</t>
+          <t>Salário-hora = salário base ÷ 220. Hora extra = salário-hora × 1,5. Adicional noturno = salário-hora × 20%. Feriado trabalhado sem folga = 1 salário-dia a mais (salário base ÷ 30).</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>As linhas em branco são para acrescentar ocorrências: preencha funcionário, ocorrência, quantidade, valor unitário e a rubrica de destino (HORAS EXTRAS ou ADICIONAL NOTURNO).</t>
+          <t>No salário de R$ 1.621,00: 40 horas extras dão R$ 442,09 e 24 horas dão R$ 265,25 — é a mesma conta usada na planilha de julho.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
+          <t>As linhas em branco são para acrescentar ocorrências: preencha funcionário, ocorrência, quantidade, valor unitário e a rubrica de destino (HORAS EXTRAS ou ADICIONAL NOTURNO).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
           <t>Os totais desta aba entram sozinhos nas linhas HORAS EXTRAS e ADICIONAL NOTURNO da aba HOLERITE SET.26.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I13"/>
+  <autoFilter ref="A4:I14"/>
   <mergeCells count="6">
+    <mergeCell ref="A19:I19"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A19:I19"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A17:I17"/>
     <mergeCell ref="A18:I18"/>
-    <mergeCell ref="A16:I16"/>
+    <mergeCell ref="A20:I20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
